--- a/LCL_Access_Matrix_2026.xlsx
+++ b/LCL_Access_Matrix_2026.xlsx
@@ -2445,14 +2445,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="Y15" s="8" t="inlineStr">
@@ -3387,14 +3387,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="W21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y21" s="8" t="inlineStr">
@@ -3603,9 +3603,9 @@
           <t>Fill / Edit Monthly KPI Data</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -10187,14 +10187,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W71" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="X71" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X71" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y71" s="8" t="inlineStr">
@@ -10344,9 +10344,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W72" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="W72" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="X72" s="8" t="inlineStr">

--- a/LCL_Access_Matrix_2026.xlsx
+++ b/LCL_Access_Matrix_2026.xlsx
@@ -6054,14 +6054,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -6211,14 +6211,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -7631,19 +7631,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q53" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="S53" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -7691,19 +7691,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AD53" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="AE53" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="AC53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -7788,19 +7788,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="R54" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="S54" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -7848,19 +7848,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC54" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AD54" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="AE54" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="AC54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -13057,14 +13057,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC91" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AD91" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="AC91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AE91" s="8" t="inlineStr">

--- a/LCL_Access_Matrix_2026.xlsx
+++ b/LCL_Access_Matrix_2026.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE100"/>
+  <dimension ref="A1:AE96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5976,7 +5976,7 @@
     <row r="42" ht="14" customHeight="1">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Kiln Form — View</t>
+          <t>CPP Form — View</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -6039,14 +6039,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="P42" s="8" t="inlineStr">
@@ -6054,14 +6054,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q42" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Q42" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
@@ -6130,177 +6130,27 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Cement Mill Form — View</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AE43" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>DAILY ENTRY FORMS — SUBMIT / EDIT</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>CPP Form — View</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Dispatch Form — Submit/Edit</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -6323,14 +6173,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J44" s="8" t="inlineStr">
@@ -6353,14 +6203,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="N44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P44" s="8" t="inlineStr">
@@ -6398,19 +6248,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W44" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X44" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y44" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="Y44" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
         </is>
       </c>
       <c r="Z44" s="8" t="inlineStr">
@@ -6428,33 +6278,183 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AE44" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="AC44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE44" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>DAILY ENTRY FORMS — SUBMIT / EDIT</t>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Stoppage Form — Submit/Edit</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="R45" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE45" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Dispatch Form — Submit/Edit</t>
+          <t>Limestone Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -6562,34 +6562,34 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W46" s="4" t="inlineStr">
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z46" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="X46" s="5" t="inlineStr">
+      <c r="AA46" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="Y46" s="5" t="inlineStr">
+      <c r="AB46" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="Z46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="AC46" s="8" t="inlineStr">
@@ -6611,7 +6611,7 @@
     <row r="47" ht="14" customHeight="1">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Stoppage Form — Submit/Edit</t>
+          <t>Quality Report Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -6689,86 +6689,86 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
+      <c r="Q47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB47" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC47" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="R47" s="5" t="inlineStr">
+      <c r="AD47" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="S47" s="5" t="inlineStr">
+      <c r="AE47" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE47" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>Limestone Form — Submit/Edit</t>
+          <t>Pile Quality Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -6891,41 +6891,41 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z48" s="4" t="inlineStr">
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB48" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC48" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="AA48" s="5" t="inlineStr">
+      <c r="AD48" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="AB48" s="5" t="inlineStr">
+      <c r="AE48" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="AC48" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD48" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE48" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Quality Report Form — Submit/Edit</t>
+          <t>Materials (Stores) Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -6973,19 +6973,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
@@ -7063,26 +7063,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC49" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AD49" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="AE49" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="AC49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE49" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>Pile Quality Form — Submit/Edit</t>
+          <t>Power Consumption Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -7160,19 +7160,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q50" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R50" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S50" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="R50" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>ENTRY</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -7220,26 +7220,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC50" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AD50" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="AE50" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="AC50" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD50" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE50" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Materials (Stores) Form — Submit/Edit</t>
+          <t>CPP Form — Submit/Edit</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -7287,36 +7287,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>ENTRY</t>
         </is>
       </c>
-      <c r="N51" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O51" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P51" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q51" s="8" t="inlineStr">
         <is>
           <t>—</t>
@@ -7393,177 +7393,27 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="14" t="inlineStr">
-        <is>
-          <t>Power Consumption Form — Submit/Edit</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="R52" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="S52" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>MIS — HR TAB</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Kiln Form — Submit/Edit</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>HR Tab — Access</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -7571,14 +7421,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -7586,14 +7436,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
@@ -7631,24 +7481,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="R53" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T53" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="U53" s="8" t="inlineStr">
@@ -7710,17 +7560,17 @@
     <row r="54" ht="14" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Cement Mill Form — Submit/Edit</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Workforce Strength — View</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -7728,14 +7578,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -7743,14 +7593,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
@@ -7788,24 +7638,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="R54" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S54" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T54" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="U54" s="8" t="inlineStr">
@@ -7867,12 +7717,12 @@
     <row r="55" ht="14" customHeight="1">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>CPP Form — Submit/Edit</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Workforce Strength — Edit</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -7885,14 +7735,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
@@ -7930,19 +7780,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr">
-        <is>
-          <t>ENTRY</t>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P55" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Q55" s="8" t="inlineStr">
@@ -8021,27 +7871,177 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>MIS — HR TAB</t>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Contractor Roster — View</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE56" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>HR Tab — Access</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Contractor Roster — Edit</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -8049,9 +8049,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -8064,14 +8064,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
@@ -8124,9 +8124,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T57" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="U57" s="8" t="inlineStr">
@@ -8188,7 +8188,7 @@
     <row r="58" ht="14" customHeight="1">
       <c r="A58" s="14" t="inlineStr">
         <is>
-          <t>Workforce Strength — View</t>
+          <t>Contractors — View</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -8345,12 +8345,12 @@
     <row r="59" ht="14" customHeight="1">
       <c r="A59" s="14" t="inlineStr">
         <is>
-          <t>Workforce Strength — Edit</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+          <t>Contractors — Edit</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -8502,7 +8502,7 @@
     <row r="60" ht="14" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>Contractor Roster — View</t>
+          <t>CSR Activities — View</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -8659,7 +8659,7 @@
     <row r="61" ht="14" customHeight="1">
       <c r="A61" s="14" t="inlineStr">
         <is>
-          <t>Contractor Roster — Edit</t>
+          <t>CSR Activities — Edit / Add</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
@@ -8813,177 +8813,27 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="14" t="inlineStr">
-        <is>
-          <t>Contractors — View</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="G62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T62" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE62" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>MIS — ASSETS TAB</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Contractors — Edit</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Assets Tab — Access</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -8991,14 +8841,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
@@ -9006,14 +8856,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J63" s="8" t="inlineStr">
@@ -9036,14 +8886,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="P63" s="8" t="inlineStr">
@@ -9051,14 +8901,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="S63" s="8" t="inlineStr">
@@ -9066,14 +8916,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="V63" s="8" t="inlineStr">
@@ -9081,14 +8931,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X63" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="Y63" s="8" t="inlineStr">
@@ -9130,7 +8980,7 @@
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>CSR Activities — View</t>
+          <t>IT Assets — View</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -9148,14 +8998,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -9193,14 +9043,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="P64" s="8" t="inlineStr">
@@ -9208,14 +9058,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="S64" s="8" t="inlineStr">
@@ -9228,9 +9078,9 @@
           <t>VIEW</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="V64" s="8" t="inlineStr">
@@ -9287,7 +9137,7 @@
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="14" t="inlineStr">
         <is>
-          <t>CSR Activities — Edit / Add</t>
+          <t>IT Assets — Edit</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -9305,89 +9155,89 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S65" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="U65" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="V65" s="8" t="inlineStr">
@@ -9441,27 +9291,177 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>MIS — ASSETS TAB</t>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Vehicles — View</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R66" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="S66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="Y66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE66" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>Assets Tab — Access</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Vehicles — Edit</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -9484,14 +9484,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
@@ -9514,14 +9514,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P67" s="8" t="inlineStr">
@@ -9529,14 +9529,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="R67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S67" s="8" t="inlineStr">
@@ -9544,14 +9544,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="U67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U67" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V67" s="8" t="inlineStr">
@@ -9559,14 +9559,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="X67" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="W67" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="X67" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="Y67" s="8" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>IT Assets — View</t>
+          <t>Spares (Assets) — View</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -9706,9 +9706,9 @@
           <t>VIEW</t>
         </is>
       </c>
-      <c r="U68" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="U68" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V68" s="8" t="inlineStr">
@@ -9765,7 +9765,7 @@
     <row r="69" ht="14" customHeight="1">
       <c r="A69" s="14" t="inlineStr">
         <is>
-          <t>IT Assets — Edit</t>
+          <t>Spares (Assets) — Edit</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
@@ -9858,14 +9858,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T69" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="U69" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="T69" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V69" s="8" t="inlineStr">
@@ -9922,7 +9922,7 @@
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Vehicles — View</t>
+          <t>CAPEX — View</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -10015,9 +10015,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T70" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T70" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="U70" s="8" t="inlineStr">
@@ -10030,14 +10030,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W70" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="X70" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="W70" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X70" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y70" s="8" t="inlineStr">
@@ -10079,12 +10079,12 @@
     <row r="71" ht="14" customHeight="1">
       <c r="A71" s="14" t="inlineStr">
         <is>
-          <t>Vehicles — Edit</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CAPEX — Edit / Approve</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
@@ -10112,14 +10112,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
@@ -10172,9 +10172,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T71" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="U71" s="8" t="inlineStr">
@@ -10187,14 +10187,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W71" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="X71" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X71" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y71" s="8" t="inlineStr">
@@ -10236,7 +10236,7 @@
     <row r="72" ht="14" customHeight="1">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Spares (Assets) — View</t>
+          <t>Land &amp; Property — View</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -10299,14 +10299,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P72" s="8" t="inlineStr">
@@ -10314,14 +10314,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q72" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R72" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S72" s="8" t="inlineStr">
@@ -10393,12 +10393,12 @@
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Spares (Assets) — Edit</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Land &amp; Property — Edit</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -10456,9 +10456,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O73" s="8" t="inlineStr">
@@ -10471,9 +10471,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="R73" s="8" t="inlineStr">
@@ -10547,177 +10547,27 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="14" t="inlineStr">
-        <is>
-          <t>CAPEX — View</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="P74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="S74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T74" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="U74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE74" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>MIS — COMPLIANCE TAB</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
       <c r="A75" s="14" t="inlineStr">
         <is>
-          <t>CAPEX — Edit / Approve</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Compliance Tab — Access</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="D75" s="8" t="inlineStr">
@@ -10725,14 +10575,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G75" s="8" t="inlineStr">
@@ -10740,9 +10590,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
@@ -10770,14 +10620,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="P75" s="8" t="inlineStr">
@@ -10785,14 +10635,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="S75" s="8" t="inlineStr">
@@ -10800,9 +10650,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T75" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="T75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="U75" s="8" t="inlineStr">
@@ -10815,14 +10665,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="Y75" s="8" t="inlineStr">
@@ -10830,14 +10680,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA75" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="AB75" s="8" t="inlineStr">
@@ -10864,7 +10714,7 @@
     <row r="76" ht="14" customHeight="1">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>Land &amp; Property — View</t>
+          <t>Certificates — View</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -10882,14 +10732,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G76" s="8" t="inlineStr">
@@ -10927,14 +10777,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="P76" s="8" t="inlineStr">
@@ -10942,14 +10792,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="S76" s="8" t="inlineStr">
@@ -10972,14 +10822,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="X76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="Y76" s="8" t="inlineStr">
@@ -10987,14 +10837,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Z76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AA76" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="AB76" s="8" t="inlineStr">
@@ -11021,32 +10871,32 @@
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>Land &amp; Property — Edit</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
+          <t>Certificates — Edit / Upload</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G77" s="8" t="inlineStr">
@@ -11084,9 +10934,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="O77" s="8" t="inlineStr">
@@ -11099,9 +10949,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="R77" s="8" t="inlineStr">
@@ -11129,9 +10979,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W77" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="X77" s="8" t="inlineStr">
@@ -11144,9 +10994,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z77" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Z77" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="AA77" s="8" t="inlineStr">
@@ -11175,27 +11025,177 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>MIS — COMPLIANCE TAB</t>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Mining Permits &amp; Licences — View</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AA78" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AB78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE78" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
       <c r="A79" s="14" t="inlineStr">
         <is>
-          <t>Compliance Tab — Access</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Mining Permits &amp; Licences — Edit</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -11203,14 +11203,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G79" s="8" t="inlineStr">
@@ -11218,14 +11218,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J79" s="8" t="inlineStr">
@@ -11248,14 +11248,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="N79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P79" s="8" t="inlineStr">
@@ -11263,14 +11263,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="R79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr">
@@ -11278,9 +11278,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="U79" s="8" t="inlineStr">
@@ -11293,14 +11293,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="X79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="W79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X79" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y79" s="8" t="inlineStr">
@@ -11308,9 +11308,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z79" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z79" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="AA79" s="3" t="inlineStr">
@@ -11342,7 +11342,7 @@
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Certificates — View</t>
+          <t>Legal Cases — View</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -11405,14 +11405,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O80" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P80" s="8" t="inlineStr">
@@ -11420,14 +11420,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R80" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S80" s="8" t="inlineStr">
@@ -11499,7 +11499,7 @@
     <row r="81" ht="14" customHeight="1">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>Certificates — Edit / Upload</t>
+          <t>Legal Cases — Edit</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -11562,9 +11562,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N81" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O81" s="8" t="inlineStr">
@@ -11577,9 +11577,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q81" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="R81" s="8" t="inlineStr">
@@ -11656,7 +11656,7 @@
     <row r="82" ht="14" customHeight="1">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>Mining Permits &amp; Licences — View</t>
+          <t>Insurance — View</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -11674,14 +11674,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
@@ -11719,14 +11719,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="P82" s="8" t="inlineStr">
@@ -11734,14 +11734,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr">
@@ -11764,14 +11764,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X82" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="X82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="Y82" s="8" t="inlineStr">
@@ -11779,14 +11779,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z82" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AA82" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AA82" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="AB82" s="8" t="inlineStr">
@@ -11813,7 +11813,7 @@
     <row r="83" ht="14" customHeight="1">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>Mining Permits &amp; Licences — Edit</t>
+          <t>Insurance — Edit / Add Claim</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
@@ -11831,14 +11831,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="G83" s="8" t="inlineStr">
@@ -11846,14 +11846,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
@@ -11876,9 +11876,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="O83" s="8" t="inlineStr">
@@ -11891,9 +11891,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="R83" s="8" t="inlineStr">
@@ -11921,9 +11921,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W83" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="W83" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="X83" s="8" t="inlineStr">
@@ -11936,14 +11936,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z83" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AA83" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z83" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AA83" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB83" s="8" t="inlineStr">
@@ -11967,177 +11967,27 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="14" t="inlineStr">
-        <is>
-          <t>Legal Cases — View</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T84" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="U84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W84" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="X84" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="Y84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z84" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AA84" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AB84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE84" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>MIS — STORE TAB</t>
         </is>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>Legal Cases — Edit</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Store Tab — Access</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
@@ -12145,14 +11995,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G85" s="8" t="inlineStr">
@@ -12160,14 +12010,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
@@ -12175,14 +12025,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="M85" s="8" t="inlineStr">
@@ -12190,14 +12040,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr">
@@ -12205,14 +12055,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="R85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr">
@@ -12220,9 +12070,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="U85" s="8" t="inlineStr">
@@ -12235,9 +12085,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W85" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="W85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="X85" s="8" t="inlineStr">
@@ -12250,14 +12100,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z85" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AA85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Z85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AA85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="AB85" s="8" t="inlineStr">
@@ -12265,14 +12115,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD85" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="AC85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AD85" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="AE85" s="8" t="inlineStr">
@@ -12284,7 +12134,7 @@
     <row r="86" ht="14" customHeight="1">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Insurance — View</t>
+          <t>Raw Materials — View</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -12302,14 +12152,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -12332,14 +12182,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="M86" s="8" t="inlineStr">
@@ -12347,14 +12197,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P86" s="8" t="inlineStr">
@@ -12362,14 +12212,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S86" s="8" t="inlineStr">
@@ -12392,14 +12242,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="X86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="W86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X86" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="Y86" s="8" t="inlineStr">
@@ -12407,14 +12257,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AA86" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Z86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AA86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="AB86" s="8" t="inlineStr">
@@ -12422,14 +12272,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD86" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="AC86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AD86" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="AE86" s="8" t="inlineStr">
@@ -12441,7 +12291,7 @@
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>Insurance — Edit / Add Claim</t>
+          <t>Raw Materials — Edit</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
@@ -12459,163 +12309,313 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="G87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z87" s="4" t="inlineStr">
         <is>
           <t>EDIT</t>
         </is>
       </c>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="6" t="inlineStr">
+      <c r="AA87" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="AB87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE87" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Spare Parts (Store) — View</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="M88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="6" t="inlineStr">
         <is>
           <t>OWN</t>
         </is>
       </c>
-      <c r="O87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q87" s="6" t="inlineStr">
+      <c r="O88" s="6" t="inlineStr">
         <is>
           <t>OWN</t>
         </is>
       </c>
-      <c r="R87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W87" s="6" t="inlineStr">
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q88" s="6" t="inlineStr">
         <is>
           <t>OWN</t>
         </is>
       </c>
-      <c r="X87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z87" s="6" t="inlineStr">
+      <c r="R88" s="6" t="inlineStr">
         <is>
           <t>OWN</t>
         </is>
       </c>
-      <c r="AA87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE87" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="13" t="inlineStr">
-        <is>
-          <t>MIS — STORE TAB</t>
+      <c r="S88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T88" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Z88" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AA88" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AB88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC88" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AD88" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AE88" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>Store Tab — Access</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Spare Parts (Store) — Edit</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -12638,14 +12638,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -12653,9 +12653,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
@@ -12668,14 +12668,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr">
@@ -12683,14 +12683,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="R89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S89" s="8" t="inlineStr">
@@ -12698,9 +12698,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="U89" s="8" t="inlineStr">
@@ -12728,14 +12728,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AA89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z89" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AA89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB89" s="8" t="inlineStr">
@@ -12743,14 +12743,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AD89" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="AC89" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="AD89" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AE89" s="8" t="inlineStr">
@@ -12762,7 +12762,7 @@
     <row r="90" ht="14" customHeight="1">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>Raw Materials — View</t>
+          <t>AMC Contracts — View</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -12825,14 +12825,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="P90" s="8" t="inlineStr">
@@ -12840,14 +12840,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q90" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R90" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr">
@@ -12885,14 +12885,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z90" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AA90" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB90" s="8" t="inlineStr">
@@ -12900,14 +12900,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC90" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="AD90" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="AC90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD90" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AE90" s="8" t="inlineStr">
@@ -12919,7 +12919,7 @@
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>Raw Materials — Edit</t>
+          <t>AMC Contracts — Edit</t>
         </is>
       </c>
       <c r="B91" s="8" t="inlineStr">
@@ -12982,9 +12982,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="O91" s="8" t="inlineStr">
@@ -12997,9 +12997,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q91" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>OWN</t>
         </is>
       </c>
       <c r="R91" s="8" t="inlineStr">
@@ -13042,14 +13042,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z91" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="AA91" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="Z91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA91" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AB91" s="8" t="inlineStr">
@@ -13073,177 +13073,27 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="14" t="inlineStr">
-        <is>
-          <t>Spare Parts (Store) — View</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="D92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="M92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="P92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="S92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T92" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="U92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AA92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AB92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AD92" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="AE92" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>GLOBAL FUNCTIONS</t>
         </is>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>Spare Parts (Store) — Edit</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Export Reports  (Excel / PDF)</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -13251,14 +13101,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
         </is>
       </c>
       <c r="G93" s="8" t="inlineStr">
@@ -13266,14 +13116,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
         </is>
       </c>
       <c r="J93" s="8" t="inlineStr">
@@ -13281,9 +13131,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K93" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
+      <c r="K93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
@@ -13296,9 +13146,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N93" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O93" s="8" t="inlineStr">
@@ -13311,9 +13161,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q93" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="R93" s="8" t="inlineStr">
@@ -13326,9 +13176,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T93" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T93" s="7" t="inlineStr">
+        <is>
+          <t>PRINT</t>
         </is>
       </c>
       <c r="U93" s="8" t="inlineStr">
@@ -13356,9 +13206,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Z93" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Z93" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AA93" s="8" t="inlineStr">
@@ -13371,9 +13221,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AC93" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="AC93" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AD93" s="8" t="inlineStr">
@@ -13390,17 +13240,17 @@
     <row r="94" ht="14" customHeight="1">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>AMC Contracts — View</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+          <t>Manage Users  (User Administration)</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -13423,14 +13273,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="J94" s="8" t="inlineStr">
@@ -13438,14 +13288,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="L94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="K94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="M94" s="8" t="inlineStr">
@@ -13453,14 +13303,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N94" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="O94" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="P94" s="8" t="inlineStr">
@@ -13468,14 +13318,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q94" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
-        </is>
-      </c>
-      <c r="R94" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R94" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="S94" s="8" t="inlineStr">
@@ -13483,9 +13333,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T94" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="T94" s="4" t="inlineStr">
+        <is>
+          <t>EDIT</t>
         </is>
       </c>
       <c r="U94" s="8" t="inlineStr">
@@ -13547,12 +13397,12 @@
     <row r="95" ht="14" customHeight="1">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>AMC Contracts — Edit</t>
-        </is>
-      </c>
-      <c r="B95" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>View Audit Log</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
@@ -13595,14 +13445,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K95" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="M95" s="8" t="inlineStr">
@@ -13610,9 +13460,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="N95" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="N95" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="O95" s="8" t="inlineStr">
@@ -13625,9 +13475,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q95" s="6" t="inlineStr">
-        <is>
-          <t>OWN</t>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="R95" s="8" t="inlineStr">
@@ -13640,14 +13490,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="T95" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U95" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="T95" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
+        </is>
+      </c>
+      <c r="U95" s="3" t="inlineStr">
+        <is>
+          <t>VIEW</t>
         </is>
       </c>
       <c r="V95" s="8" t="inlineStr">
@@ -13701,636 +13551,158 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>GLOBAL FUNCTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="14" t="inlineStr">
-        <is>
-          <t>Export Reports  (Excel / PDF)</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Print Reports</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
+      <c r="D96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="F97" s="7" t="inlineStr">
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="J97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K97" s="7" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="L97" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="M97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T97" s="7" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="U97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE97" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="14" t="inlineStr">
-        <is>
-          <t>Manage Users  (User Administration)</t>
-        </is>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T98" s="4" t="inlineStr">
-        <is>
-          <t>EDIT</t>
-        </is>
-      </c>
-      <c r="U98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE98" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="14" t="inlineStr">
-        <is>
-          <t>View Audit Log</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="T99" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="U99" s="3" t="inlineStr">
-        <is>
-          <t>VIEW</t>
-        </is>
-      </c>
-      <c r="V99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE99" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="14" t="inlineStr">
-        <is>
-          <t>Print Reports</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="J96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="C100" s="7" t="inlineStr">
+      <c r="K96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="D100" s="7" t="inlineStr">
+      <c r="L96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="E100" s="7" t="inlineStr">
+      <c r="M96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
+      <c r="N96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="G100" s="7" t="inlineStr">
+      <c r="O96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
+      <c r="P96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="Q96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="R96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="K100" s="7" t="inlineStr">
+      <c r="S96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="L100" s="7" t="inlineStr">
+      <c r="T96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="M100" s="7" t="inlineStr">
+      <c r="U96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="N100" s="7" t="inlineStr">
+      <c r="V96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="O100" s="7" t="inlineStr">
+      <c r="W96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="P100" s="7" t="inlineStr">
+      <c r="X96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="Q100" s="7" t="inlineStr">
+      <c r="Y96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="R100" s="7" t="inlineStr">
+      <c r="Z96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="S100" s="7" t="inlineStr">
+      <c r="AA96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="T100" s="7" t="inlineStr">
+      <c r="AB96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="U100" s="7" t="inlineStr">
+      <c r="AC96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="V100" s="7" t="inlineStr">
+      <c r="AD96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
       </c>
-      <c r="W100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="X100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="Y100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="Z100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="AA100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="AB100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="AC100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="AD100" s="7" t="inlineStr">
-        <is>
-          <t>PRINT</t>
-        </is>
-      </c>
-      <c r="AE100" s="7" t="inlineStr">
+      <c r="AE96" s="7" t="inlineStr">
         <is>
           <t>PRINT</t>
         </is>
@@ -14348,19 +13720,19 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="T2:V2"/>
     <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="A62:AE62"/>
     <mergeCell ref="E2:G2"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A96:AE96"/>
+    <mergeCell ref="A43:AE43"/>
+    <mergeCell ref="A52:AE52"/>
+    <mergeCell ref="A92:AE92"/>
     <mergeCell ref="A30:AE30"/>
     <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A34:AE34"/>
     <mergeCell ref="W2:Y2"/>
     <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="A45:AE45"/>
-    <mergeCell ref="A88:AE88"/>
-    <mergeCell ref="A78:AE78"/>
-    <mergeCell ref="A66:AE66"/>
-    <mergeCell ref="A56:AE56"/>
+    <mergeCell ref="A84:AE84"/>
+    <mergeCell ref="A74:AE74"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
